--- a/Result/profitability/5481.xlsx
+++ b/Result/profitability/5481.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1425</v>
+        <v>-0.1724999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>36.08624999999999</v>
+        <v>36.52499999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2162499999999999</v>
+        <v>-0.2187499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>29.77124999999999</v>
+        <v>30.91749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2787499999999999</v>
+        <v>-0.2799999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>24.66374999999999</v>
+        <v>25.03124999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4012499999999999</v>
+        <v>-0.3674999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>16.35624999999999</v>
+        <v>17.01124999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>-0.4625</v>
       </c>
       <c r="N6" t="n">
-        <v>8.927499999999991</v>
+        <v>9.304999999999993</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.83</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5499999999999999</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>2.929999999999993</v>
+        <v>5.718749999999992</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.53875</v>
+        <v>-0.5425</v>
       </c>
       <c r="N8" t="n">
-        <v>1.061249999999992</v>
+        <v>1.162499999999993</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.5462499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.626250000000008</v>
+        <v>-4.626250000000007</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4574999999999999</v>
+        <v>-0.4575</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.120000000000007</v>
+        <v>-3.120000000000006</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3137499999999999</v>
+        <v>-0.31375</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3937500000000069</v>
+        <v>-0.393750000000006</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.2712499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3175000000000071</v>
+        <v>-0.3175000000000062</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.2449999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3849999999999927</v>
+        <v>0.3849999999999936</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5481</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-31.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1112499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.80499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8100000000000023</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01728184339662908</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.675</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.240000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1234684260131951</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
